--- a/safety_inspection_forms/019_safety_compliance_checklist_access_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/019_safety_compliance_checklist_access_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="41" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -520,41 +520,45 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>title</t>
+          <t>form_title</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>safety_compliance_checklist_access_form</t>
+          <t>Form Title</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>purpose</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>categories</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>Purpose of the Safety Compliance Checklist</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please describe the purpose of the Safety Compliance Checklist</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -566,64 +570,72 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>responsible_officer</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Responsible Officer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Name and designation of the officer responsible for the checklist</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>inspection_areas</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Inspection Areas</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>inspection_schedule</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Inspection Schedule</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Date of the last inspection</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -635,15 +647,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>incident_reporting</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>Incident Reporting</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Procedures for reporting and documenting safety incidents</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
           <t>yes</t>
@@ -653,17 +669,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>safety_training</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>Safety Training</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,23 +692,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>safety_records</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>Safety Records Maintenance</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,35 +720,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>non_compliance_consequences</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Non-Compliance Consequences</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Consequences of non-compliance with safety standards</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>incident_reporting_process</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>Incident Reporting Process</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +765,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>safety_officer_role</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>Role of Safety Officer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,322 +788,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>safety_compliance_monitoring</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>assigned_form_id</t>
+          <t>Safety Compliance Monitoring</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
           <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>assigned_form_id</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
         </is>
       </c>
     </row>
@@ -1098,12 +819,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,68 +847,425 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>inspection_areas_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>safety_inspection_forms</t>
+          <t>fire_safety</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Safety Inspection Forms</t>
+          <t>Fire Safety</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>inspection_areas_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>administrative_forms</t>
+          <t>electrical_safety</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Administrative Forms</t>
+          <t>Electrical Safety</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>inspection_areas_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chemical_safety</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Chemical Safety</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>inspection_areas_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>emergency_equipment</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Emergency Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>inspection_areas_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>personal_protective_equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Personal Protective Equipment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>safety_training_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>on-the-job</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>On-the-job</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>safety_training_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>class_room</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Class Room</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>safety_training_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>online_course</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Online Course</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>safety_training_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>safety_records_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>maintenance_records</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Maintenance Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>safety_records_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>incident_records</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Incident Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>safety_records_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>training_records</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Training Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>safety_records_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>certification_records</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Certification Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>incident_reporting_process_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>immediate_reporting</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Immediate Reporting</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>incident_reporting_process_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>investigation</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Investigation</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>incident_reporting_process_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reporting_to_authorities</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Reporting to Authorities</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>incident_reporting_process_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Others</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>safety_officer_role_choices</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>conducting_training</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Conducting Training</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>safety_officer_role_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>conducting_inspections</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Conducting Inspections</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>safety_officer_role_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>maintaining_records</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Maintaining Records</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>safety_officer_role_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>coordinating_with_authorities</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Coordinating with Authorities</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>safety_compliance_monitoring_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>regular_inspections</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Regular Inspections</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>safety_compliance_monitoring_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>audits</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Audits</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>safety_compliance_monitoring_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>certification</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>safety_compliance_monitoring_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>others</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Others</t>
         </is>
       </c>
     </row>
